--- a/think3d_repro/outputs/run2/vlmeval_runs/SPAgent_4B_no_tools_general/MindCube/SPAgent_4B_no_tools_general_MindCube.xlsx
+++ b/think3d_repro/outputs/run2/vlmeval_runs/SPAgent_4B_no_tools_general/MindCube/SPAgent_4B_no_tools_general_MindCube.xlsx
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>9.367327690124512</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3132,7 +3132,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>6.927553415298462</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3161,7 +3161,7 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>5.701394081115723</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3190,7 +3190,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>30.23545551300049</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3219,7 +3219,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>6.99096417427063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3248,7 +3248,7 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>11.24364614486694</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3277,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>10.32112503051758</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -3306,7 +3306,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>4.985543727874756</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -3335,7 +3335,7 @@
         <v>1</v>
       </c>
       <c r="I10">
-        <v>3.787032127380371</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -3364,7 +3364,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>8.121977806091309</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -3393,7 +3393,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>37.20954895019531</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -3422,7 +3422,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>34.7705979347229</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -3451,7 +3451,7 @@
         <v>1</v>
       </c>
       <c r="I14">
-        <v>6.774847745895386</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -3480,7 +3480,7 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>5.469926118850708</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -3509,7 +3509,7 @@
         <v>1</v>
       </c>
       <c r="I16">
-        <v>28.35893821716309</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -3538,7 +3538,7 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>13.74875831604004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -3567,7 +3567,7 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>11.87499713897705</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -3596,7 +3596,7 @@
         <v>1</v>
       </c>
       <c r="I19">
-        <v>8.565830707550049</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>7.343298673629761</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -3654,7 +3654,7 @@
         <v>1</v>
       </c>
       <c r="I21">
-        <v>4.280884265899658</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -3683,7 +3683,7 @@
         <v>1</v>
       </c>
       <c r="I22">
-        <v>19.67896699905396</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -3712,7 +3712,7 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>5.761957168579102</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>4.934033632278442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -3770,7 +3770,7 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>13.77044534683228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -3799,7 +3799,7 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>27.77490854263306</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -3828,7 +3828,7 @@
         <v>1</v>
       </c>
       <c r="I27">
-        <v>7.212323665618896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -3857,7 +3857,7 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>7.820067882537842</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -3886,7 +3886,7 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>8.849642276763916</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>34.12552690505981</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>6.771680593490601</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -3973,7 +3973,7 @@
         <v>1</v>
       </c>
       <c r="I32">
-        <v>34.33954358100891</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -4002,7 +4002,7 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>5.709151029586792</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -4031,7 +4031,7 @@
         <v>1</v>
       </c>
       <c r="I34">
-        <v>4.218772411346436</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -4060,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>5.652928113937378</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -4089,7 +4089,7 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>11.49172234535217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -4118,7 +4118,7 @@
         <v>0</v>
       </c>
       <c r="I37">
-        <v>5.089329481124878</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -4147,7 +4147,7 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>6.665564060211182</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -4176,7 +4176,7 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>7.114842891693115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -4205,7 +4205,7 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>11.68688297271729</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -4234,7 +4234,7 @@
         <v>0</v>
       </c>
       <c r="I41">
-        <v>4.623141527175903</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -4263,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>3.712712526321411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -4292,7 +4292,7 @@
         <v>0</v>
       </c>
       <c r="I43">
-        <v>4.718541145324707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -4321,7 +4321,7 @@
         <v>1</v>
       </c>
       <c r="I44">
-        <v>5.252622842788696</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -4350,7 +4350,7 @@
         <v>1</v>
       </c>
       <c r="I45">
-        <v>2.689702272415161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -4379,7 +4379,7 @@
         <v>0</v>
       </c>
       <c r="I46">
-        <v>5.345422267913818</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -4408,7 +4408,7 @@
         <v>1</v>
       </c>
       <c r="I47">
-        <v>2.952491998672485</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -4437,7 +4437,7 @@
         <v>0</v>
       </c>
       <c r="I48">
-        <v>6.750294923782349</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -4466,7 +4466,7 @@
         <v>0</v>
       </c>
       <c r="I49">
-        <v>2.951627969741821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -4495,7 +4495,7 @@
         <v>0</v>
       </c>
       <c r="I50">
-        <v>3.790924549102783</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -4524,7 +4524,7 @@
         <v>0</v>
       </c>
       <c r="I51">
-        <v>4.253101825714111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -4553,7 +4553,7 @@
         <v>0</v>
       </c>
       <c r="I52">
-        <v>6.292183399200439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -4582,7 +4582,7 @@
         <v>0</v>
       </c>
       <c r="I53">
-        <v>5.662639617919922</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -4611,7 +4611,7 @@
         <v>0</v>
       </c>
       <c r="I54">
-        <v>3.020901679992676</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -4640,7 +4640,7 @@
         <v>0</v>
       </c>
       <c r="I55">
-        <v>3.302932024002075</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -4669,7 +4669,7 @@
         <v>0</v>
       </c>
       <c r="I56">
-        <v>4.877916812896729</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -4698,7 +4698,7 @@
         <v>1</v>
       </c>
       <c r="I57">
-        <v>3.569326877593994</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -4727,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="I58">
-        <v>3.262887477874756</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -4756,7 +4756,7 @@
         <v>1</v>
       </c>
       <c r="I59">
-        <v>2.79438591003418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -4785,7 +4785,7 @@
         <v>1</v>
       </c>
       <c r="I60">
-        <v>3.48766040802002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -4814,7 +4814,7 @@
         <v>0</v>
       </c>
       <c r="I61">
-        <v>3.818724870681763</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -4843,7 +4843,7 @@
         <v>1</v>
       </c>
       <c r="I62">
-        <v>4.380944490432739</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -4872,7 +4872,7 @@
         <v>1</v>
       </c>
       <c r="I63">
-        <v>2.209038019180298</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -4901,7 +4901,7 @@
         <v>1</v>
       </c>
       <c r="I64">
-        <v>15.17258763313293</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -4930,7 +4930,7 @@
         <v>1</v>
       </c>
       <c r="I65">
-        <v>5.71400260925293</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -4959,7 +4959,7 @@
         <v>1</v>
       </c>
       <c r="I66">
-        <v>3.369074821472168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -4988,7 +4988,7 @@
         <v>0</v>
       </c>
       <c r="I67">
-        <v>4.787409782409668</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -5017,7 +5017,7 @@
         <v>0</v>
       </c>
       <c r="I68">
-        <v>5.654067039489746</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -5046,7 +5046,7 @@
         <v>1</v>
       </c>
       <c r="I69">
-        <v>9.277884006500244</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -5075,7 +5075,7 @@
         <v>1</v>
       </c>
       <c r="I70">
-        <v>5.264431953430176</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -5104,7 +5104,7 @@
         <v>1</v>
       </c>
       <c r="I71">
-        <v>4.001607894897461</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -5133,7 +5133,7 @@
         <v>1</v>
       </c>
       <c r="I72">
-        <v>3.116024494171143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -5162,7 +5162,7 @@
         <v>1</v>
       </c>
       <c r="I73">
-        <v>4.777509927749634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -5191,7 +5191,7 @@
         <v>1</v>
       </c>
       <c r="I74">
-        <v>3.968415975570679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -5220,7 +5220,7 @@
         <v>1</v>
       </c>
       <c r="I75">
-        <v>5.849141597747803</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -5249,7 +5249,7 @@
         <v>0</v>
       </c>
       <c r="I76">
-        <v>4.187254428863525</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -5278,7 +5278,7 @@
         <v>0</v>
       </c>
       <c r="I77">
-        <v>8.402593374252319</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -5307,7 +5307,7 @@
         <v>0</v>
       </c>
       <c r="I78">
-        <v>4.103821277618408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -5336,7 +5336,7 @@
         <v>0</v>
       </c>
       <c r="I79">
-        <v>6.265475273132324</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -5365,7 +5365,7 @@
         <v>0</v>
       </c>
       <c r="I80">
-        <v>5.378060817718506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -5394,7 +5394,7 @@
         <v>0</v>
       </c>
       <c r="I81">
-        <v>3.486536741256714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -5423,7 +5423,7 @@
         <v>1</v>
       </c>
       <c r="I82">
-        <v>5.886521816253662</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -5452,7 +5452,7 @@
         <v>0</v>
       </c>
       <c r="I83">
-        <v>6.559961080551147</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -5481,7 +5481,7 @@
         <v>0</v>
       </c>
       <c r="I84">
-        <v>5.075267314910889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -5510,7 +5510,7 @@
         <v>1</v>
       </c>
       <c r="I85">
-        <v>3.946612119674683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -5539,7 +5539,7 @@
         <v>0</v>
       </c>
       <c r="I86">
-        <v>5.206993579864502</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -5568,7 +5568,7 @@
         <v>1</v>
       </c>
       <c r="I87">
-        <v>10.01293182373047</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -5597,7 +5597,7 @@
         <v>0</v>
       </c>
       <c r="I88">
-        <v>5.433760643005371</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -5626,7 +5626,7 @@
         <v>0</v>
       </c>
       <c r="I89">
-        <v>5.731069803237915</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -5655,7 +5655,7 @@
         <v>0</v>
       </c>
       <c r="I90">
-        <v>7.079858064651489</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -5684,7 +5684,7 @@
         <v>0</v>
       </c>
       <c r="I91">
-        <v>8.45400071144104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -5713,7 +5713,7 @@
         <v>0</v>
       </c>
       <c r="I92">
-        <v>5.666446924209595</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -5742,7 +5742,7 @@
         <v>1</v>
       </c>
       <c r="I93">
-        <v>2.520462989807129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -5771,7 +5771,7 @@
         <v>0</v>
       </c>
       <c r="I94">
-        <v>4.005598545074463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -5800,7 +5800,7 @@
         <v>0</v>
       </c>
       <c r="I95">
-        <v>5.474052667617798</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -5829,7 +5829,7 @@
         <v>0</v>
       </c>
       <c r="I96">
-        <v>7.1580970287323</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -5858,7 +5858,7 @@
         <v>1</v>
       </c>
       <c r="I97">
-        <v>16.70707964897156</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -5887,7 +5887,7 @@
         <v>1</v>
       </c>
       <c r="I98">
-        <v>7.785744428634644</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -5916,7 +5916,7 @@
         <v>0</v>
       </c>
       <c r="I99">
-        <v>8.634784460067749</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -5945,7 +5945,7 @@
         <v>0</v>
       </c>
       <c r="I100">
-        <v>4.985393285751343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -5974,7 +5974,7 @@
         <v>0</v>
       </c>
       <c r="I101">
-        <v>3.976327180862427</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -6003,7 +6003,7 @@
         <v>1</v>
       </c>
       <c r="I102">
-        <v>5.357853412628174</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -6032,7 +6032,7 @@
         <v>0</v>
       </c>
       <c r="I103">
-        <v>10.90671110153198</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -6061,7 +6061,7 @@
         <v>1</v>
       </c>
       <c r="I104">
-        <v>5.403095245361328</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -6090,7 +6090,7 @@
         <v>0</v>
       </c>
       <c r="I105">
-        <v>5.365105152130127</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -6119,7 +6119,7 @@
         <v>0</v>
       </c>
       <c r="I106">
-        <v>6.245753765106201</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -6148,7 +6148,7 @@
         <v>0</v>
       </c>
       <c r="I107">
-        <v>7.470767736434937</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -6177,7 +6177,7 @@
         <v>0</v>
       </c>
       <c r="I108">
-        <v>8.657279968261719</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -6206,7 +6206,7 @@
         <v>0</v>
       </c>
       <c r="I109">
-        <v>5.040721654891968</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -6235,7 +6235,7 @@
         <v>1</v>
       </c>
       <c r="I110">
-        <v>4.507001638412476</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -6264,7 +6264,7 @@
         <v>0</v>
       </c>
       <c r="I111">
-        <v>4.649062395095825</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -6293,7 +6293,7 @@
         <v>1</v>
       </c>
       <c r="I112">
-        <v>5.932134628295898</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -6322,7 +6322,7 @@
         <v>0</v>
       </c>
       <c r="I113">
-        <v>3.952489614486694</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -6351,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="I114">
-        <v>4.445289134979248</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -6380,7 +6380,7 @@
         <v>1</v>
       </c>
       <c r="I115">
-        <v>6.50465202331543</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -6409,7 +6409,7 @@
         <v>0</v>
       </c>
       <c r="I116">
-        <v>5.286690473556519</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -6438,7 +6438,7 @@
         <v>0</v>
       </c>
       <c r="I117">
-        <v>7.444965362548828</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -6467,7 +6467,7 @@
         <v>0</v>
       </c>
       <c r="I118">
-        <v>6.093961715698242</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -6496,7 +6496,7 @@
         <v>1</v>
       </c>
       <c r="I119">
-        <v>5.952367544174194</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -6525,7 +6525,7 @@
         <v>1</v>
       </c>
       <c r="I120">
-        <v>5.453880786895752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -6554,7 +6554,7 @@
         <v>0</v>
       </c>
       <c r="I121">
-        <v>6.653848171234131</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
